--- a/LISTAS/ma/BARRAL DE SEGURIDAD PARA BAÑO DISMAY.xlsx
+++ b/LISTAS/ma/BARRAL DE SEGURIDAD PARA BAÑO DISMAY.xlsx
@@ -755,14 +755,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="18" t="n">
-        <v>45163.60817047113</v>
+        <v>45253</v>
       </c>
       <c r="E1" s="7" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -808,26 +804,6 @@
       </c>
       <c r="E11" s="12" t="n"/>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
     <row r="32" ht="18" customHeight="1" s="1">
       <c r="A32" s="20" t="inlineStr">
         <is>
@@ -859,7 +835,7 @@
       </c>
       <c r="C33" s="26" t="n"/>
       <c r="D33" s="27" t="n">
-        <v>3593.75</v>
+        <v>3773.438</v>
       </c>
       <c r="E33" s="28" t="n"/>
       <c r="F33" s="28" t="n"/>
@@ -877,7 +853,7 @@
       </c>
       <c r="C34" s="26" t="n"/>
       <c r="D34" s="27" t="n">
-        <v>4252.5</v>
+        <v>4465.125</v>
       </c>
       <c r="E34" s="28" t="n"/>
       <c r="F34" s="28" t="n"/>
@@ -895,7 +871,7 @@
       </c>
       <c r="C35" s="26" t="n"/>
       <c r="D35" s="29" t="n">
-        <v>5252.5</v>
+        <v>5515.125</v>
       </c>
       <c r="E35" s="28" t="n"/>
       <c r="F35" s="28" t="n"/>
@@ -913,7 +889,7 @@
       </c>
       <c r="C36" s="26" t="n"/>
       <c r="D36" s="29" t="n">
-        <v>5858.75</v>
+        <v>6151.688</v>
       </c>
       <c r="E36" s="28" t="n"/>
       <c r="F36" s="28" t="n"/>
@@ -931,7 +907,7 @@
       </c>
       <c r="C37" s="26" t="n"/>
       <c r="D37" s="29" t="n">
-        <v>6058.75</v>
+        <v>6361.688</v>
       </c>
       <c r="E37" s="28" t="n"/>
       <c r="F37" s="28" t="n"/>
@@ -942,20 +918,6 @@
     <row r="39" ht="18" customHeight="1" s="1">
       <c r="E39" s="4" t="n"/>
     </row>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
     <row r="54" ht="15.75" customHeight="1" s="1">
       <c r="A54" s="5" t="n"/>
     </row>
@@ -964,16 +926,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
     <mergeCell ref="B37:C37"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A10:D10"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B36:C36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/BARRAL DE SEGURIDAD PARA BAÑO DISMAY.xlsx
+++ b/LISTAS/ma/BARRAL DE SEGURIDAD PARA BAÑO DISMAY.xlsx
@@ -755,7 +755,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="18" t="n">
-        <v>45253</v>
+        <v>45254</v>
       </c>
       <c r="E1" s="7" t="n"/>
     </row>

--- a/LISTAS/ma/BARRAL DE SEGURIDAD PARA BAÑO DISMAY.xlsx
+++ b/LISTAS/ma/BARRAL DE SEGURIDAD PARA BAÑO DISMAY.xlsx
@@ -755,7 +755,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="18" t="n">
-        <v>45254</v>
+        <v>45255</v>
       </c>
       <c r="E1" s="7" t="n"/>
     </row>

--- a/LISTAS/ma/BARRAL DE SEGURIDAD PARA BAÑO DISMAY.xlsx
+++ b/LISTAS/ma/BARRAL DE SEGURIDAD PARA BAÑO DISMAY.xlsx
@@ -755,7 +755,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="18" t="n">
-        <v>45255</v>
+        <v>45256</v>
       </c>
       <c r="E1" s="7" t="n"/>
     </row>

--- a/LISTAS/ma/BARRAL DE SEGURIDAD PARA BAÑO DISMAY.xlsx
+++ b/LISTAS/ma/BARRAL DE SEGURIDAD PARA BAÑO DISMAY.xlsx
@@ -755,7 +755,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="18" t="n">
-        <v>45256</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="7" t="n"/>
     </row>

--- a/LISTAS/ma/BARRAL DE SEGURIDAD PARA BAÑO DISMAY.xlsx
+++ b/LISTAS/ma/BARRAL DE SEGURIDAD PARA BAÑO DISMAY.xlsx
@@ -755,10 +755,14 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="18" t="n">
-        <v>45266</v>
+        <v>45264.64766643339</v>
       </c>
       <c r="E1" s="7" t="n"/>
     </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -804,6 +808,26 @@
       </c>
       <c r="E11" s="12" t="n"/>
     </row>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
     <row r="32" ht="18" customHeight="1" s="1">
       <c r="A32" s="20" t="inlineStr">
         <is>
@@ -835,7 +859,7 @@
       </c>
       <c r="C33" s="26" t="n"/>
       <c r="D33" s="27" t="n">
-        <v>3773.438</v>
+        <v>5858.26</v>
       </c>
       <c r="E33" s="28" t="n"/>
       <c r="F33" s="28" t="n"/>
@@ -853,7 +877,7 @@
       </c>
       <c r="C34" s="26" t="n"/>
       <c r="D34" s="27" t="n">
-        <v>4465.125</v>
+        <v>6932.1</v>
       </c>
       <c r="E34" s="28" t="n"/>
       <c r="F34" s="28" t="n"/>
@@ -871,7 +895,7 @@
       </c>
       <c r="C35" s="26" t="n"/>
       <c r="D35" s="29" t="n">
-        <v>5515.125</v>
+        <v>8562.23</v>
       </c>
       <c r="E35" s="28" t="n"/>
       <c r="F35" s="28" t="n"/>
@@ -889,7 +913,7 @@
       </c>
       <c r="C36" s="26" t="n"/>
       <c r="D36" s="29" t="n">
-        <v>6151.688</v>
+        <v>9550.49</v>
       </c>
       <c r="E36" s="28" t="n"/>
       <c r="F36" s="28" t="n"/>
@@ -907,7 +931,7 @@
       </c>
       <c r="C37" s="26" t="n"/>
       <c r="D37" s="29" t="n">
-        <v>6361.688</v>
+        <v>9876.52</v>
       </c>
       <c r="E37" s="28" t="n"/>
       <c r="F37" s="28" t="n"/>
@@ -918,6 +942,20 @@
     <row r="39" ht="18" customHeight="1" s="1">
       <c r="E39" s="4" t="n"/>
     </row>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
     <row r="54" ht="15.75" customHeight="1" s="1">
       <c r="A54" s="5" t="n"/>
     </row>
@@ -926,16 +964,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B37:C37"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B32:C32"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B37:C37"/>
     <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B35:C35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>
